--- a/data/trans_orig/IP3102-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3102-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15897</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9851</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37863</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43460</t>
+          <t>43264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>63600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70351</t>
+          <t>69787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70030</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>109179</t>
+          <t>108892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136367</t>
+          <t>134394</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22126</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37278</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44545</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66025</t>
+          <t>65119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>19774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>34887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>22620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43382</t>
+          <t>42887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24305</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>40534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57368</t>
+          <t>58231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69137</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92994</t>
+          <t>92623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51125</t>
+          <t>51734</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70935</t>
+          <t>70858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60440</t>
+          <t>60332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81305</t>
+          <t>82093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>116688</t>
+          <t>116191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145928</t>
+          <t>146411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56051</t>
+          <t>56174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51912</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76899</t>
+          <t>77281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102459</t>
+          <t>103475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36964</t>
+          <t>38032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>58631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24054</t>
+          <t>24194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40159</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60888</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>54684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41661</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59953</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83600</t>
+          <t>81713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>108152</t>
+          <t>105908</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>36489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>37369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47171</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>15247</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>28271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>41847</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60943</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15725</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>27741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45024</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63072</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>70043</t>
+          <t>68639</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92200</t>
+          <t>92839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60430</t>
+          <t>61629</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82898</t>
+          <t>83310</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136791</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170203</t>
+          <t>169381</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>54680</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38295</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78983</t>
+          <t>78930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107645</t>
+          <t>105096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15292</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60021</t>
+          <t>59795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34452</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>71105</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100559</t>
+          <t>99930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97230</t>
+          <t>96656</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>127570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129354</t>
+          <t>129458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163352</t>
+          <t>163789</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>235004</t>
+          <t>234811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>281372</t>
+          <t>280244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>225609</t>
+          <t>227257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>266540</t>
+          <t>266659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>233366</t>
+          <t>233365</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>273953</t>
+          <t>274022</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>470996</t>
+          <t>472320</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>528303</t>
+          <t>527924</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>131988</t>
+          <t>132657</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>167528</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>129523</t>
+          <t>129273</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>162575</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>271462</t>
+          <t>271538</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>318194</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>74750</t>
+          <t>76187</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101520</t>
+          <t>103828</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>98495</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>152838</t>
+          <t>151291</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>190490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37571</t>
+          <t>36510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46777</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54741</t>
+          <t>54539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79082</t>
+          <t>78352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52340</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>33953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52884</t>
+          <t>52730</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72715</t>
+          <t>71655</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98120</t>
+          <t>96928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31301</t>
+          <t>31646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40330</t>
+          <t>40279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>62005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40779</t>
+          <t>41037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54852</t>
+          <t>55140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78229</t>
+          <t>79104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31673</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47967</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>40559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60224</t>
+          <t>60584</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76702</t>
+          <t>76033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102429</t>
+          <t>102003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44965</t>
+          <t>45441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64751</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50392</t>
+          <t>51322</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71916</t>
+          <t>72575</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100744</t>
+          <t>102047</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>130511</t>
+          <t>131579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42981</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82393</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40326</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60916</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58067</t>
+          <t>57000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84357</t>
+          <t>83108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38776</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30444</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58854</t>
+          <t>57724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81009</t>
+          <t>80916</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39826</t>
+          <t>39420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57555</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54962</t>
+          <t>55627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82987</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107519</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31876</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>34937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>53680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29198</t>
+          <t>29873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45541</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27079</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>42755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61244</t>
+          <t>61279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>85074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36025</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>33848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42955</t>
+          <t>41407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>64904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50435</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>72515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52264</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72396</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108122</t>
+          <t>108694</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>138371</t>
+          <t>139570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44577</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>23030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>41134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78491</t>
+          <t>77700</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>53660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76368</t>
+          <t>75597</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>55937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78493</t>
+          <t>79511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114916</t>
+          <t>115663</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146489</t>
+          <t>145662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61130</t>
+          <t>62537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142320</t>
+          <t>142094</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>133805</t>
+          <t>133394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>169348</t>
+          <t>168715</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251082</t>
+          <t>252045</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>299324</t>
+          <t>301011</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>188382</t>
+          <t>187137</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>227391</t>
+          <t>226750</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>191838</t>
+          <t>194622</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>231284</t>
+          <t>234076</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>391897</t>
+          <t>393009</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>449479</t>
+          <t>449533</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>96802</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>127675</t>
+          <t>126998</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>99373</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>131266</t>
+          <t>132303</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>203881</t>
+          <t>206858</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>250253</t>
+          <t>252061</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169007</t>
+          <t>167508</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>205638</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>162598</t>
+          <t>161637</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>199227</t>
+          <t>200645</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>342288</t>
+          <t>341140</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>395051</t>
+          <t>394364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26888</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40643</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27306</t>
+          <t>26958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>37043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51412</t>
+          <t>50856</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75829</t>
+          <t>74291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>38019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57586</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82721</t>
+          <t>82718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29868</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46914</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56301</t>
+          <t>56942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>72737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99273</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32656</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>49629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66900</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93289</t>
+          <t>93541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57312</t>
+          <t>56556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57774</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81753</t>
+          <t>80905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108509</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31530</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49321</t>
+          <t>48988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54901</t>
+          <t>54966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71263</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97480</t>
+          <t>97826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>48236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68257</t>
+          <t>67303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>58188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>80317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112073</t>
+          <t>112262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143310</t>
+          <t>141571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>31265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>29866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30460</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>35769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>54995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33064</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49588</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39305</t>
+          <t>39716</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57444</t>
+          <t>58537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75671</t>
+          <t>76119</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>100962</t>
+          <t>100030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>38214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34864</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67758</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34049</t>
+          <t>34728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>51278</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>58468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79470</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104694</t>
+          <t>103325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>31554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>42405</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65765</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>30569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49531</t>
+          <t>49759</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>39182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59732</t>
+          <t>60544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73087</t>
+          <t>74002</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101548</t>
+          <t>101481</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37822</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59067</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36321</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>56054</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79153</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106456</t>
+          <t>106337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57899</t>
+          <t>57168</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80754</t>
+          <t>78917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49110</t>
+          <t>49183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69863</t>
+          <t>70158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112281</t>
+          <t>113515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>142095</t>
+          <t>144391</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81446</t>
+          <t>80574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>94474</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>126790</t>
+          <t>125340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>86202</t>
+          <t>84412</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115603</t>
+          <t>114874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>187369</t>
+          <t>188046</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>233575</t>
+          <t>231128</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>143910</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180718</t>
+          <t>180375</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>153954</t>
+          <t>154622</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190250</t>
+          <t>192230</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>307403</t>
+          <t>306613</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>359559</t>
+          <t>361253</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127943</t>
+          <t>128768</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>163555</t>
+          <t>163144</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>138435</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>178121</t>
+          <t>175069</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>279093</t>
+          <t>279524</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>329100</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>185992</t>
+          <t>187938</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>225191</t>
+          <t>226371</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>204427</t>
+          <t>205997</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>245682</t>
+          <t>245394</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>402280</t>
+          <t>403639</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>459367</t>
+          <t>459626</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
